--- a/artfynd/A 26217-2026 artfynd.xlsx
+++ b/artfynd/A 26217-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1995775</v>
+        <v>801194</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584811.3786855481</v>
+        <v>584811</v>
       </c>
       <c r="R2" t="n">
-        <v>7111620.582260256</v>
+        <v>7111621</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2005-10-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>801194</v>
+        <v>1995775</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584810.5039564021</v>
+        <v>584811</v>
       </c>
       <c r="R3" t="n">
-        <v>7111620.558330171</v>
+        <v>7111621</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,19 +845,9 @@
           <t>2005-10-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
